--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -3485,7 +3485,7 @@
         <v>131199884</v>
       </c>
       <c r="B25" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -3485,7 +3485,7 @@
         <v>131199884</v>
       </c>
       <c r="B25" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
